--- a/TestFiles-prod-sanity/AdvanceAndAdjustment/[MLB]AdvanceStatement-AA.xlsx
+++ b/TestFiles-prod-sanity/AdvanceAndAdjustment/[MLB]AdvanceStatement-AA.xlsx
@@ -91,7 +91,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>ATENA-ADV-AA-TEST-A028</t>
+    <t>ATENA-ADV-AA-TEST-A044</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
@@ -100,7 +100,7 @@
     <t>IL</t>
   </si>
   <si>
-    <t>test-aetna-aca-test-advance-month-july-21</t>
+    <t>test-aetna-aca-advance-july-21</t>
   </si>
   <si>
     <t>Y</t>
